--- a/output/pdf_financials_xlsx/XIM.xlsx
+++ b/output/pdf_financials_xlsx/XIM.xlsx
@@ -6169,31 +6169,31 @@
         <v>0.565161</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.701885</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.71557</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.07358000000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.617341</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.416761</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.7639</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.800918</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.939087</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.029645</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -6201,16 +6201,16 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.785184</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.303051</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.196918</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.14975</v>
       </c>
     </row>
     <row r="93">
@@ -7677,16 +7677,16 @@
         <v>0.322993</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>4.548964</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>2.362527</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.83675</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>0.925575</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0</v>
@@ -10149,7 +10149,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12644,7 +12648,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -14351,7 +14359,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -28421,7 +28433,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -32780,7 +32796,11 @@
           <t>Share-Based Payment Reserve 73,580</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -35299,7 +35319,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -35398,7 +35422,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -36588,7 +36616,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -36685,7 +36717,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -44135,7 +44171,11 @@
           <t>Shares Issued for Exploration and Evaluation Expenditures</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -45709,7 +45749,11 @@
           <t>Exploration and Evaluation Expenditures</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XIM.xlsx
+++ b/output/pdf_financials_xlsx/XIM.xlsx
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.3e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.150206</v>
+        <v>-1.150219</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.149449</v>
+        <v>-2.149476</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.365585</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.150206</v>
+        <v>-1.150219</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.149449</v>
+        <v>-2.149476</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.364885</v>
@@ -2485,13 +2485,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.163577</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.081007</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -2509,19 +2507,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.076294</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.202846</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022988</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.041164</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.718573</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2529,16 +2527,16 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.453309</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.003864</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000933</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001184</v>
       </c>
     </row>
     <row r="35">
@@ -2609,13 +2607,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.163577</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.081007</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2633,19 +2629,19 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.076294</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.22</v>
+        <v>0.422846</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.067871</v>
+        <v>0.090859</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.364847</v>
+        <v>0.406011</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.156914</v>
+        <v>0.875487</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2653,16 +2649,16 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.09455</v>
+        <v>0.547859</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.023973</v>
+        <v>0.027837</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000933</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001184</v>
       </c>
     </row>
     <row r="37">
@@ -3359,7 +3355,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.097094</v>
+        <v>0.016087</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.254046</v>
@@ -3377,19 +3373,19 @@
         <v>0.09655</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.079067</v>
+        <v>0.002773</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.234768</v>
+        <v>0.031922</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.247041</v>
+        <v>0.224053</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.586978</v>
+        <v>0.545814</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.810667</v>
+        <v>1.092094</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -3397,16 +3393,16 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.118469</v>
+        <v>0.66516</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.135309</v>
+        <v>0.131445</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.078789</v>
+        <v>0.07785599999999999</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.03527</v>
+        <v>0.034086</v>
       </c>
     </row>
     <row r="49">
@@ -8982,7 +8978,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -39875,7 +39871,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E312" s="5" t="n">
@@ -68067,7 +68063,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">

--- a/output/pdf_financials_xlsx/XIM.xlsx
+++ b/output/pdf_financials_xlsx/XIM.xlsx
@@ -761,10 +761,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.263065</v>
+        <v>0.375065</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.155078</v>
+        <v>0.266999</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.07016500000000001</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.263065</v>
+        <v>0.375065</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.155078</v>
+        <v>0.266999</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.187644</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.263065</v>
+        <v>-0.375065</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.685947</v>
@@ -2492,7 +2492,7 @@
         <v>0.081007</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.158162</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.025107</v>
@@ -2614,7 +2614,7 @@
         <v>0.081007</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.158162</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.025107</v>
@@ -3358,7 +3358,7 @@
         <v>0.016087</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.254046</v>
+        <v>0.095884</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.196052</v>
@@ -3999,16 +3999,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0.005045</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.412977</v>
+        <v>0.418</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.870479</v>
+        <v>0.874841</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>0.0375</v>
@@ -4511,19 +4509,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0.03574</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.01316</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0</v>
+        <v>0.087254</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0</v>
+        <v>0.242733</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>0</v>
@@ -4710,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -4834,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -5395,10 +5391,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="3" t="n">
+        <v>-0.09287766628066445</v>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
@@ -5915,13 +5909,13 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>2.734633</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>4.148395</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>5.060052</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>0</v>
@@ -34917,7 +34911,11 @@
           <t>Loans payable- Note 9</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -35727,7 +35725,11 @@
           <t>Cash – Note 5 $</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -35921,7 +35923,11 @@
           <t>Due from related parties – Note 10</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -36018,7 +36024,11 @@
           <t>Property and equipment – Note 7</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -36216,7 +36226,11 @@
           <t>Due to related parties – Note 10</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36414,7 +36428,11 @@
           <t>Share capital – Note 9</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -36818,7 +36836,11 @@
           <t>Cash – Note 3 $</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -37016,7 +37038,11 @@
           <t>Due from related parties – Note 7</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -37115,7 +37141,11 @@
           <t>Property and equipment – Note 4</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -37313,7 +37343,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -40071,7 +40105,11 @@
           <t>Due from related parties – Note 6</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -40172,7 +40210,11 @@
           <t>Property and equipment – Note 3</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>0.005045</v>
       </c>
@@ -40370,7 +40412,11 @@
           <t>Due to related parties – Note 6</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E317" s="5" t="n">
         <v>0.03574</v>
       </c>
@@ -67055,7 +67101,11 @@
           <t>Consulting fees- Note 9</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -69271,7 +69321,11 @@
           <t>Management fees – Note 10</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XIM.xlsx
+++ b/output/pdf_financials_xlsx/XIM.xlsx
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.375065</v>
+        <v>0.405065</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.266999</v>
+        <v>0.296999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.07016500000000001</v>
+        <v>0.08766500000000001</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.168729</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.375065</v>
+        <v>0.405065</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.266999</v>
+        <v>0.296999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.187644</v>
+        <v>0.205144</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.6221179999999999</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.375065</v>
+        <v>-0.405065</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.685947</v>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.150206</v>
+        <v>-0.948878</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-2.149449</v>
+        <v>-1.877824</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-0.365585</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.201328</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.271625</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.150219</v>
+        <v>-0.948891</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.149476</v>
+        <v>-1.877851</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.365585</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.150219</v>
+        <v>-0.948891</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.149476</v>
+        <v>-1.877851</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.364885</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-21.21748001323668</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.46488062779046</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -6651,55 +6651,55 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002409</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.003857</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.032364</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.018033</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.00165</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.094234</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-0.09639</v>
+        <v>-0.004959</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009162999999999999</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004749</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.03483</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.000357</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>-0.019406</v>
+        <v>-0.020525</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0.371666</v>
+        <v>0.357708</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0.003</v>
+        <v>0.008011000000000001</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>0.02225</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>-0.101741</v>
+        <v>-0.092191</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0.08908199999999999</v>
+        <v>0.092432</v>
       </c>
     </row>
     <row r="102">
@@ -6956,40 +6956,40 @@
         <v>-0.101564</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.152078</v>
+        <v>0.057844</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.770375</v>
+        <v>0.861806</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.037016</v>
+        <v>-0.046179</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.057379</v>
+        <v>-0.062128</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.039665</v>
+        <v>-0.07449500000000001</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.319225</v>
+        <v>0.319582</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.488276</v>
+        <v>-0.489395</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.194208</v>
+        <v>0.18025</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.294843</v>
+        <v>-0.289832</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>1.308557</v>
+        <v>1.330807</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1.189177</v>
+        <v>1.198727</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.535575</v>
+        <v>0.538925</v>
       </c>
     </row>
     <row r="107">
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.014802</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -7490,25 +7490,25 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.199299</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.267865</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.0796</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.023973</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -41839,7 +41839,11 @@
           <t>GST Recoverable</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -42464,7 +42468,11 @@
           <t>Proceeds from Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -49583,7 +49591,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -53545,7 +53557,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -53941,7 +53957,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E456" s="5" t="n">
         <v>-0.002409</v>
       </c>
@@ -65485,7 +65505,11 @@
           <t>Director Fees</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
           <t>-</t>
@@ -67204,7 +67228,11 @@
           <t>Director fees- Note 9</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
@@ -68511,7 +68539,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
           <t>-</t>
@@ -69222,7 +69254,11 @@
           <t>Director’s fees – Note 10</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
